--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484692_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484692_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5593</v>
+        <v>6.7164</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9549</v>
+        <v>5.9138</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.8025</v>
       </c>
       <c r="G2" t="n">
         <v>2.5744</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3083</v>
+        <v>-0.1512</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0717</v>
+        <v>0.0306</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.38</v>
+        <v>-0.1818</v>
       </c>
       <c r="V2" t="n">
         <v>1.9109</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9471</v>
+        <v>4.6192</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9568</v>
+        <v>3.1491</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9903</v>
+        <v>1.4701</v>
       </c>
       <c r="G3" t="n">
         <v>0.7449</v>
@@ -688,13 +688,13 @@
         <v>3.6651</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1251</v>
+        <v>-0.4531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6606</v>
+        <v>-0.4683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5355</v>
+        <v>0.0153</v>
       </c>
       <c r="V3" t="n">
         <v>1.5785</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4224</v>
+        <v>4.2415</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6295</v>
+        <v>4.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2071</v>
+        <v>-0.0585</v>
       </c>
       <c r="G4" t="n">
         <v>0.9447</v>
@@ -766,13 +766,13 @@
         <v>3.2986</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0433</v>
+        <v>-0.1376</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5845</v>
+        <v>0.2549</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5412</v>
+        <v>-0.3925</v>
       </c>
       <c r="V4" t="n">
         <v>3.8009</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9724</v>
+        <v>3.9691</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3815</v>
+        <v>4.725</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4091</v>
+        <v>-0.7559</v>
       </c>
       <c r="G5" t="n">
         <v>3.718</v>
@@ -844,13 +844,13 @@
         <v>2.5656</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1549</v>
+        <v>0.1516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4593</v>
+        <v>-0.1157</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6142</v>
+        <v>0.2673</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0012</v>
+        <v>1.9601</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5101</v>
+        <v>2.469</v>
       </c>
       <c r="F7" t="n">
         <v>-0.5089</v>
@@ -1000,10 +1000,10 @@
         <v>2.7489</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0551</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0536</v>
+        <v>0.0125</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1086</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5321</v>
+        <v>1.6367</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1934</v>
+        <v>1.2484</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3388</v>
+        <v>0.3883</v>
       </c>
       <c r="G8" t="n">
         <v>1.1876</v>
@@ -1078,13 +1078,13 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3885</v>
+        <v>-0.2839</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2202</v>
+        <v>-0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1683</v>
+        <v>-0.1188</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4522</v>
+        <v>1.2846</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2277</v>
+        <v>-0.42</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6798</v>
+        <v>1.7046</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0093</v>
@@ -1156,13 +1156,13 @@
         <v>3.2986</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1628</v>
+        <v>-0.0047</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1818</v>
+        <v>-0.0105</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0189</v>
+        <v>0.0058</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3599</v>
+        <v>0.3381</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0667</v>
+        <v>-0.1629</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4266</v>
+        <v>0.5009</v>
       </c>
       <c r="G11" t="n">
         <v>1.0622</v>
@@ -1312,13 +1312,13 @@
         <v>2.3823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3358</v>
+        <v>-0.3576</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1086</v>
+        <v>0.0125</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4444</v>
+        <v>-0.3701</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2907</v>
+        <v>-0.0925</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6859</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3952</v>
+        <v>0.5933</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2208</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4365</v>
+        <v>-0.2383</v>
       </c>
       <c r="T12" t="n">
         <v>-0.3122</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1243</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9605</v>
+        <v>-1.4024</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.477</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4835</v>
+        <v>-1.3101</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9289</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8195</v>
+        <v>-0.2615</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5505</v>
+        <v>-0.1659</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.269</v>
+        <v>-0.0956</v>
       </c>
       <c r="V13" t="n">
         <v>0.3219</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.7963</v>
+        <v>27.0717</v>
       </c>
       <c r="E14" t="n">
-        <v>23.9698</v>
+        <v>24.2451</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8264</v>
+        <v>2.826299999999999</v>
       </c>
       <c r="G14" t="n">
         <v>10.9691</v>
@@ -1546,13 +1546,13 @@
         <v>24.7396</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1078</v>
+        <v>-1.8325</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2026</v>
+        <v>-0.9273</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.905</v>
+        <v>-0.9051000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>6.0233</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.755100000000001</v>
+        <v>7.4894</v>
       </c>
       <c r="E15" t="n">
-        <v>9.218</v>
+        <v>7.968</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5371</v>
+        <v>-0.4786</v>
       </c>
       <c r="G15" t="n">
         <v>2.2701</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0347</v>
+        <v>1.769</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9947</v>
+        <v>0.7447</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>1.0243</v>
       </c>
       <c r="V15" t="n">
         <v>2.5339</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8769</v>
+        <v>-0.4296</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4105</v>
+        <v>0.5067</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2874</v>
+        <v>-0.9363</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4464</v>
@@ -1702,13 +1702,13 @@
         <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3468</v>
+        <v>0.1005</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4223</v>
+        <v>-0.3262</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0755</v>
+        <v>0.4267</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1086</v>
+        <v>-0.4297</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1363</v>
+        <v>2.6171</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.245</v>
+        <v>-3.0468</v>
       </c>
       <c r="G17" t="n">
         <v>0.2803</v>
@@ -1780,13 +1780,13 @@
         <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4727</v>
+        <v>0.2063</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2391</v>
+        <v>0.2417</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2336</v>
+        <v>-0.0355</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1673</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2.01</v>
+        <v>2.1061</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1773</v>
+        <v>-2.8466</v>
       </c>
       <c r="G18" t="n">
         <v>0.3435</v>
@@ -1858,13 +1858,13 @@
         <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6103</v>
+        <v>-0.1834</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0188</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5915</v>
+        <v>-0.2608</v>
       </c>
       <c r="V18" t="n">
         <v>-1.267</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6637</v>
+        <v>-2.9454</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2695</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9332</v>
+        <v>-3.5034</v>
       </c>
       <c r="G19" t="n">
         <v>2.0247</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7275</v>
+        <v>-0.0092</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4774</v>
+        <v>-0.1889</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2502</v>
+        <v>0.1797</v>
       </c>
       <c r="V19" t="n">
         <v>-2.212</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6934</v>
+        <v>-5.3452</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0381</v>
+        <v>-3.942</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6553</v>
+        <v>-1.4032</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7888</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.339</v>
+        <v>0.0092</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3122</v>
+        <v>-0.2161</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0268</v>
+        <v>0.2253</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7999</v>
+        <v>-5.5325</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1259</v>
+        <v>-4.3969</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.674</v>
+        <v>-1.1355</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7085</v>
+        <v>-3.8647</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1863</v>
+        <v>-1.7552</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8947</v>
+        <v>-2.1095</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6606</v>
+        <v>-1.0878</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5356</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.125</v>
+        <v>-0.4743</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3691</v>
+        <v>-2.7769</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3493</v>
+        <v>-1.1418</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0198</v>
+        <v>-1.6351</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6493</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9321</v>
+        <v>-3.4819</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4137</v>
+        <v>0.348</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1456</v>
+        <v>0.1727</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2682</v>
+        <v>0.1753</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9127</v>
+        <v>-5.8252</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9452</v>
+        <v>-3.2337</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9674</v>
+        <v>-2.5915</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3908</v>
@@ -2170,13 +2170,13 @@
         <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>0.494</v>
+        <v>0.5815</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6395</v>
+        <v>0.3511</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1456</v>
+        <v>0.2304</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0417</v>
+        <v>-5.8625</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7877</v>
+        <v>-3.6915</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.254</v>
+        <v>-2.171</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6886</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0684</v>
+        <v>0.2475</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0007</v>
+        <v>0.0954</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1521</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5889</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2872</v>
+        <v>-5.8932</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9739</v>
+        <v>-1.3182</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3133</v>
+        <v>-4.5749</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.8647</v>
+        <v>-1.7085</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7552</v>
+        <v>0.1863</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1095</v>
+        <v>-1.8947</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0878</v>
+        <v>1.6606</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6133999999999999</v>
+        <v>1.5356</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4743</v>
+        <v>0.125</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7769</v>
+        <v>-3.3691</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1418</v>
+        <v>-1.3493</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6351</v>
+        <v>-2.0198</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0158</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4819</v>
+        <v>-2.9321</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4066</v>
+        <v>0.3205</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4042</v>
+        <v>-0.0467</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0024</v>
+        <v>0.3673</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.8559</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.7963</v>
+        <v>-25.5143</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.826499999999999</v>
+        <v>-2.826399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.9698</v>
+        <v>-22.6878</v>
       </c>
       <c r="G25" t="n">
         <v>-10.9692</v>
@@ -2383,7 +2383,7 @@
         <v>17.0347</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1622000000000005</v>
+        <v>0.1622000000000006</v>
       </c>
       <c r="M25" t="n">
         <v>-28.166</v>
@@ -2404,16 +2404,16 @@
         <v>12.8279</v>
       </c>
       <c r="S25" t="n">
-        <v>2.107899999999999</v>
+        <v>3.3899</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9051000000000001</v>
+        <v>0.9050000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2027</v>
+        <v>2.4848</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.0234</v>
+        <v>-6.023400000000001</v>
       </c>
       <c r="W25" t="n">
         <v>3.8113</v>
